--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.58345495394668</v>
+        <v>8.057311430016336</v>
       </c>
       <c r="D2" t="n">
-        <v>49.56007193569771</v>
+        <v>8.053511689550879</v>
       </c>
       <c r="E2" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F2" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.95247573882259</v>
+        <v>5.51727730755867</v>
       </c>
       <c r="D3" t="n">
-        <v>33.96503193178674</v>
+        <v>5.519317688915345</v>
       </c>
       <c r="E3" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F3" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.91459241041385</v>
+        <v>8.436121266692252</v>
       </c>
       <c r="D4" t="n">
-        <v>51.84122387716946</v>
+        <v>8.424198880040038</v>
       </c>
       <c r="E4" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F4" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.33603074462642</v>
+        <v>4.767104996001794</v>
       </c>
       <c r="D5" t="n">
-        <v>29.3120328319532</v>
+        <v>4.763205335192396</v>
       </c>
       <c r="E5" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F5" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.04875107217466</v>
+        <v>4.720422049228383</v>
       </c>
       <c r="D6" t="n">
-        <v>29.18931912439293</v>
+        <v>4.743264357713851</v>
       </c>
       <c r="E6" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F6" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.129624807780065</v>
+        <v>0.9960640312642606</v>
       </c>
       <c r="D7" t="n">
-        <v>6.264535481578433</v>
+        <v>1.017987015756495</v>
       </c>
       <c r="E7" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F7" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.48457712151804</v>
+        <v>7.716243782246681</v>
       </c>
       <c r="D8" t="n">
-        <v>47.3623492779862</v>
+        <v>7.696381757672757</v>
       </c>
       <c r="E8" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F8" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.43441228544074</v>
+        <v>6.083091996384121</v>
       </c>
       <c r="D9" t="n">
-        <v>37.29698593236231</v>
+        <v>6.060760214008876</v>
       </c>
       <c r="E9" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F9" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.08721966126998</v>
+        <v>5.864173194956373</v>
       </c>
       <c r="D10" t="n">
-        <v>36.204471542881</v>
+        <v>5.883226625718162</v>
       </c>
       <c r="E10" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F10" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.3087749804392</v>
+        <v>7.687675934321369</v>
       </c>
       <c r="D11" t="n">
-        <v>47.16940872214892</v>
+        <v>7.665028917349201</v>
       </c>
       <c r="E11" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F11" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.36908162571938</v>
+        <v>2.659975764179399</v>
       </c>
       <c r="D12" t="n">
-        <v>16.31246176489851</v>
+        <v>2.650775036796007</v>
       </c>
       <c r="E12" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F12" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.29063812269852</v>
+        <v>6.38472869493851</v>
       </c>
       <c r="D13" t="n">
-        <v>39.15030401123342</v>
+        <v>6.361924401825432</v>
       </c>
       <c r="E13" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F13" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.41258885104646</v>
+        <v>4.45454568829505</v>
       </c>
       <c r="D14" t="n">
-        <v>27.28709980745456</v>
+        <v>4.434153718711366</v>
       </c>
       <c r="E14" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F14" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.05477703878601</v>
+        <v>6.833901268802727</v>
       </c>
       <c r="D15" t="n">
-        <v>42.12465439266511</v>
+        <v>6.845256338808081</v>
       </c>
       <c r="E15" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F15" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.72288998810762</v>
+        <v>9.37996962306749</v>
       </c>
       <c r="D16" t="n">
-        <v>57.79175980626525</v>
+        <v>9.391160968518104</v>
       </c>
       <c r="E16" t="n">
-        <v>13.31421403625632</v>
+        <v>2.163559780891652</v>
       </c>
       <c r="F16" t="n">
-        <v>13.28624468127482</v>
+        <v>2.159014760707159</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
